--- a/RU_battery_channels.xlsx
+++ b/RU_battery_channels.xlsx
@@ -1830,7 +1830,7 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Требует проверки глубокой ссылки</t>
+          <t>Категория не подтверждена: витрина только алкогольная</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>GP, Duracell, Energizer + СТМ</t>
+          <t>GP Super Alkaline, GP Ultra Alkaline, Energizer Plus Max, СТМ «Магнит Нужные вещи»</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Онлайн-витрина ограничена; региональная логика не подтверждена</t>
+          <t>Единый URL категории и карточки; ассортимент общий с группой «Магнит»</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>https://dixy.ru/</t>
+          <t>https://dixy.ru/catalog/tovary-dlya-doma-i-dachi/osveshchenie-remont-batareyki/</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Требует проверки глубокой ссылки</t>
+          <t>Проверено</t>
         </is>
       </c>
       <c r="O18" s="6" t="n">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>GP, Duracell, Energizer + СТМ</t>
+          <t>Kodak Super Heavy Duty, GP, Duracell + СТМ</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -2102,27 +2102,27 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Сеть Красноярского края, Иркутской и Кемеровской обл., Хакасии и Тывы</t>
+          <t>Онлайн-витрина вынесена на отдельный поддомен доставки; регион в URL не кодируется</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>delivery.sm-komandor.ru — поддомен доставки, не региона</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>https://sm-komandor.ru/</t>
+          <t>https://delivery.sm-komandor.ru/catalog/batareyki-akkumulyatory_193/</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Требует проверки глубокой ссылки</t>
+          <t>Проверено</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>МТС (салоны)</t>
+          <t>МТС (интернет-магазин)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>mts.ru</t>
+          <t>shop.mts.ru</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>GP, Duracell, Energizer, Varta</t>
+          <t>Duracell Professional, GP, Energizer, Varta</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>Батарейки — аксессуарная категория салонов; онлайн-витрина ограничена</t>
+          <t>Единый URL карточки, регион — селектором</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>https://www.mts.ru/</t>
+          <t>https://shop.mts.ru/product/batareja-duracell-aa-professional-lr6-bl2</t>
         </is>
       </c>
       <c r="N35" s="13" t="inlineStr">
         <is>
-          <t>Требует проверки глубокой ссылки</t>
+          <t>Проверено</t>
         </is>
       </c>
       <c r="O35" s="12" t="n">
@@ -4136,22 +4136,22 @@
       </c>
       <c r="H47" s="16" t="inlineStr">
         <is>
-          <t>GP, Duracell, Varta, Energizer</t>
+          <t>Duracell Ultra Power, CMI (СТМ), Duracell CEF14</t>
         </is>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
-          <t>Есть (СТМ Ленты)</t>
+          <t>Есть (CMI)</t>
         </is>
       </c>
       <c r="J47" s="15" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K47" s="16" t="inlineStr">
         <is>
-          <t>С 2026 идёт поэтапный ребрендинг в «Дом Лента» — структура сайта меняется</t>
+          <t>Каталог работает, единый URL категории; сеть вошла в «Ленту» и ребрендируется в «Дом Лента»</t>
         </is>
       </c>
       <c r="L47" s="16" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="M47" s="17" t="inlineStr">
         <is>
-          <t>https://www.obi.ru/</t>
+          <t>https://www.obi.ru/jelektrika/jelementy-pitanija-i-zarjadnye-ustrojstva/akkumuljatornye-batarejki</t>
         </is>
       </c>
       <c r="N47" s="16" t="inlineStr">
         <is>
-          <t>Статус меняется (ребрендинг 2026)</t>
+          <t>Проверено (сайт работает; ребрендинг 2026 продолжается)</t>
         </is>
       </c>
       <c r="O47" s="15" t="n">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H52" s="19" t="inlineStr">
         <is>
-          <t>Батарейки к приборам ухода</t>
+          <t>GP Batteries (щелочные AAA/LR03), батарейки к приборам ухода</t>
         </is>
       </c>
       <c r="I52" s="19" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="J52" s="18" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K52" s="19" t="inlineStr">
         <is>
-          <t>Батарейка — сопутствующий товар к электроприборам ухода</t>
+          <t>Единый URL карточки на РФ</t>
         </is>
       </c>
       <c r="L52" s="19" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="M52" s="20" t="inlineStr">
         <is>
-          <t>https://www.letu.ru/</t>
+          <t>https://www.letu.ru/product/gp-batteries-elementy-pitaniya-shchelochnye-aaa-lr03-/147100048</t>
         </is>
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Требует проверки глубокой ссылки</t>
+          <t>Проверено</t>
         </is>
       </c>
       <c r="O52" s="18" t="n">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="H55" s="22" t="inlineStr">
         <is>
-          <t>Батарейки как сопутствующая позиция</t>
+          <t>GoPower (солевые, щелочные, литиевые), ENERGON/Delta Battery</t>
         </is>
       </c>
       <c r="I55" s="22" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="J55" s="21" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K55" s="22" t="inlineStr">
         <is>
-          <t>Закрытый B2B-портал, публичной витрины батареек нет</t>
+          <t>B2B-каталог с разделом энергоснабжения и страницами вендоров</t>
         </is>
       </c>
       <c r="L55" s="22" t="inlineStr">
@@ -4745,12 +4745,12 @@
       </c>
       <c r="M55" s="23" t="inlineStr">
         <is>
-          <t>https://www.ocs.ru/</t>
+          <t>https://www.ocs.ru/vendors/gopower/</t>
         </is>
       </c>
       <c r="N55" s="22" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Проверено</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>opticom.ru</t>
+          <t>opti-com.ru</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
@@ -5239,29 +5239,29 @@
           <t>Есть</t>
         </is>
       </c>
-      <c r="J62" s="21" t="inlineStr">
-        <is>
-          <t>Требует уточнения</t>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Есть версии</t>
         </is>
       </c>
       <c r="K62" s="22" t="inlineStr">
         <is>
-          <t>B2B-портал; батарейки в составе хозяйственно-канцелярского ассортимента</t>
+          <t>Филиальная структура с отдельными сайтами: Москва, СПб, Сочи, Н.Новгород, Самара, Краснодар</t>
         </is>
       </c>
       <c r="L62" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>opti-com.ru (Москва) / opticom-spb.ru (СПб) / sochi.opti-com.ru</t>
         </is>
       </c>
       <c r="M62" s="23" t="inlineStr">
         <is>
-          <t>https://opticom.ru/</t>
+          <t>https://www.opti-com.ru/</t>
         </is>
       </c>
       <c r="N62" s="22" t="inlineStr">
         <is>
-          <t>Опознано по юрлицу, глубокая ссылка не проверена</t>
+          <t>Проверено (домен исправлен: opticom.ru — другая компания, телеком)</t>
         </is>
       </c>
       <c r="O62" s="21" t="n">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="K64" s="22" t="inlineStr">
         <is>
-          <t>Оптовый портал, доступ по договору</t>
+          <t>Оптовый портал подтверждён, цены после авторизации; раздел батареек не зафиксирован</t>
         </is>
       </c>
       <c r="L64" s="22" t="inlineStr">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="M64" s="23" t="inlineStr">
         <is>
-          <t>https://relefopt.ru/</t>
+          <t>https://relefopt.ru/catalog/68473/</t>
         </is>
       </c>
       <c r="N64" s="22" t="inlineStr">
         <is>
-          <t>Требует проверки глубокой ссылки</t>
+          <t>Каталог подтверждён, раздел батареек не зафиксирован</t>
         </is>
       </c>
       <c r="O64" s="21" t="n">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="H65" s="22" t="inlineStr">
         <is>
-          <t>Космос, IEK, Duracell, GP</t>
+          <t>КОСМОС, IEK, Duracell, GP</t>
         </is>
       </c>
       <c r="I65" s="22" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="J65" s="21" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K65" s="22" t="inlineStr">
         <is>
-          <t>Филиальная структура; региональная логика витрины не подтверждена</t>
+          <t>Единый портал электротехники, 850 000+ SKU; цены после авторизации</t>
         </is>
       </c>
       <c r="L65" s="22" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="M65" s="23" t="inlineStr">
         <is>
-          <t>https://www.rs24.ru/</t>
+          <t>https://rs24.ru/product/391260</t>
         </is>
       </c>
       <c r="N65" s="22" t="inlineStr">
         <is>
-          <t>Требует проверки глубокой ссылки</t>
+          <t>Проверено</t>
         </is>
       </c>
       <c r="O65" s="21" t="n">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>АБ-Бэттэрис</t>
+          <t>АБ-Бэттэрис (бренд GoPower)</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
@@ -6097,47 +6097,47 @@
       </c>
       <c r="F74" s="25" t="inlineStr">
         <is>
-          <t>Оптовый поставщик элементов питания</t>
+          <t>Производитель и дистрибьютор элементов питания</t>
         </is>
       </c>
       <c r="G74" s="25" t="inlineStr">
         <is>
-          <t>Юрлицо ООО «АБ-БЭТТЭРИС»</t>
+          <t>На рынке с 1994; собственное производство в Москве, бренд GoPower</t>
         </is>
       </c>
       <c r="H74" s="25" t="inlineStr">
         <is>
-          <t>GP, Duracell, Varta, Energizer</t>
+          <t>GoPower: солевые, щелочные, литий-диоксид-марганцевые, литий-тионилхлоридные; аккумуляторы, ЗУ</t>
         </is>
       </c>
       <c r="I74" s="25" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Есть (GoPower — собственный бренд)</t>
         </is>
       </c>
       <c r="J74" s="24" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K74" s="25" t="inlineStr">
         <is>
-          <t>Опознано по юрлицу из клиентской базы; домен требует подтверждения</t>
+          <t>Единый оптовый каталог; отдельный сайт бренда go-power.ru</t>
         </is>
       </c>
       <c r="L74" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ab-batteries.ru (опт) / go-power.ru (бренд)</t>
+        </is>
+      </c>
+      <c r="M74" s="26" t="inlineStr">
+        <is>
+          <t>https://ab-batteries.ru/catalog/elementy_pitaniya/</t>
         </is>
       </c>
       <c r="N74" s="25" t="inlineStr">
         <is>
-          <t>Не подтверждён сайт</t>
+          <t>Проверено — прямой игрок категории</t>
         </is>
       </c>
       <c r="O74" s="24" t="n">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="C77" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>batkomplekt.ru</t>
         </is>
       </c>
       <c r="D77" s="24" t="inlineStr">
@@ -6316,17 +6316,17 @@
       </c>
       <c r="F77" s="25" t="inlineStr">
         <is>
-          <t>Оптовый поставщик элементов питания</t>
+          <t>Опт электротоваров и товаров народного потребления</t>
         </is>
       </c>
       <c r="G77" s="25" t="inlineStr">
         <is>
-          <t>Юрлицо ООО «БАТКОМПЛЕКТ»</t>
+          <t>Пермь, с 1996</t>
         </is>
       </c>
       <c r="H77" s="25" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Элементы питания, аккумуляторы, фонари, лампы, мультимедиа, хозтовары</t>
         </is>
       </c>
       <c r="I77" s="25" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="J77" s="24" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K77" s="25" t="inlineStr">
         <is>
-          <t>Опознано по юрлицу; сайт не найден</t>
+          <t>Единый оптовый каталог</t>
         </is>
       </c>
       <c r="L77" s="25" t="inlineStr">
@@ -6349,14 +6349,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M77" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M77" s="26" t="inlineStr">
+        <is>
+          <t>https://www.batkomplekt.ru/</t>
         </is>
       </c>
       <c r="N77" s="25" t="inlineStr">
         <is>
-          <t>Не подтверждён сайт</t>
+          <t>Проверено</t>
         </is>
       </c>
       <c r="O77" s="24" t="n">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="C79" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>vrnbatt.ru</t>
         </is>
       </c>
       <c r="D79" s="24" t="inlineStr">
@@ -6462,17 +6462,17 @@
       </c>
       <c r="F79" s="25" t="inlineStr">
         <is>
-          <t>Региональный поставщик элементов питания</t>
+          <t>Опт элементов питания и светотехники</t>
         </is>
       </c>
       <c r="G79" s="25" t="inlineStr">
         <is>
-          <t>Юрлицо ООО «Воронеж Бэттерис»</t>
+          <t>Воронеж, ул. Чебышева 5; опт и розница</t>
         </is>
       </c>
       <c r="H79" s="25" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Duracell, Energizer, GP, Varta, Panasonic</t>
         </is>
       </c>
       <c r="I79" s="25" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="J79" s="24" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K79" s="25" t="inlineStr">
         <is>
-          <t>Опознано по юрлицу; сайт не найден</t>
+          <t>Единый каталог; опт по Воронежу и области</t>
         </is>
       </c>
       <c r="L79" s="25" t="inlineStr">
@@ -6495,14 +6495,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M79" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M79" s="26" t="inlineStr">
+        <is>
+          <t>http://vrnbatt.ru/</t>
         </is>
       </c>
       <c r="N79" s="25" t="inlineStr">
         <is>
-          <t>Не подтверждён сайт</t>
+          <t>Проверено — прямой игрок категории</t>
         </is>
       </c>
       <c r="O79" s="24" t="n">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="C81" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>istochnik.ru</t>
         </is>
       </c>
       <c r="D81" s="24" t="inlineStr">
@@ -6608,17 +6608,17 @@
       </c>
       <c r="F81" s="25" t="inlineStr">
         <is>
-          <t>Оптовый поставщик элементов питания</t>
+          <t>Федеральный дистрибьютор источников питания</t>
         </is>
       </c>
       <c r="G81" s="25" t="inlineStr">
         <is>
-          <t>Юрлицо ООО «ИСТОЧНИК БЭТТЭРИС»</t>
+          <t>Федеральная дистрибуция</t>
         </is>
       </c>
       <c r="H81" s="25" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Широкий портфель источников питания</t>
         </is>
       </c>
       <c r="I81" s="25" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="J81" s="24" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K81" s="25" t="inlineStr">
         <is>
-          <t>Опознано по юрлицу; сайт не найден</t>
+          <t>Единый федеральный каталог</t>
         </is>
       </c>
       <c r="L81" s="25" t="inlineStr">
@@ -6641,14 +6641,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M81" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M81" s="26" t="inlineStr">
+        <is>
+          <t>https://www.istochnik.ru/</t>
         </is>
       </c>
       <c r="N81" s="25" t="inlineStr">
         <is>
-          <t>Не подтверждён сайт</t>
+          <t>Проверено — прямой игрок категории</t>
         </is>
       </c>
       <c r="O81" s="24" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="H94" s="28" t="inlineStr">
         <is>
-          <t>Батарейки к фонарям, пульсометрам, электронике</t>
+          <t>ARMYTEK, Fenix, аккумуляторные батарейки к фонарям и навигации</t>
         </is>
       </c>
       <c r="I94" s="28" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="J94" s="27" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K94" s="28" t="inlineStr">
         <is>
-          <t>Батарейка — расходник к спортивным товарам</t>
+          <t>Единый URL категории, регион — селектором</t>
         </is>
       </c>
       <c r="L94" s="28" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="M94" s="29" t="inlineStr">
         <is>
-          <t>https://www.sportmaster.ru/</t>
+          <t>https://www.sportmaster.ru/catalog/vidy_sporta_/turizm/ehlektronika-i-navigaciya/akkumulyatory-i-batareyki/</t>
         </is>
       </c>
       <c r="N94" s="28" t="inlineStr">
         <is>
-          <t>Требует проверки глубокой ссылки</t>
+          <t>Проверено</t>
         </is>
       </c>
       <c r="O94" s="27" t="n">
@@ -7975,12 +7975,12 @@
       </c>
       <c r="B100" s="30" t="inlineStr">
         <is>
-          <t>Почта России</t>
+          <t>Почта России (Маркет)</t>
         </is>
       </c>
       <c r="C100" s="30" t="inlineStr">
         <is>
-          <t>pochta.ru</t>
+          <t>market.pochta.ru</t>
         </is>
       </c>
       <c r="D100" s="30" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="F100" s="31" t="inlineStr">
         <is>
-          <t>Госритейл в отделениях</t>
+          <t>Маркетплейс Почты + продажи в отделениях</t>
         </is>
       </c>
       <c r="G100" s="31" t="inlineStr">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="J100" s="30" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K100" s="31" t="inlineStr">
         <is>
-          <t>Батарейки продаются в отделениях; онлайн-витрина ограничена</t>
+          <t>Отдельный маркетплейс market.pochta.ru; в отделениях батарейки как сопутствующий товар</t>
         </is>
       </c>
       <c r="L100" s="31" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="M100" s="32" t="inlineStr">
         <is>
-          <t>https://www.pochta.ru/</t>
+          <t>https://market.pochta.ru/</t>
         </is>
       </c>
       <c r="N100" s="31" t="inlineStr">
         <is>
-          <t>Требует проверки глубокой ссылки</t>
+          <t>Маркетплейс подтверждён, раздел батареек не зафиксирован</t>
         </is>
       </c>
       <c r="O100" s="30" t="n">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H101" s="31" t="inlineStr">
         <is>
-          <t>Батарейки в прикассовой зоне АЗС</t>
+          <t>Алкалиновые AA, специальные E23A</t>
         </is>
       </c>
       <c r="I101" s="31" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="J101" s="30" t="inlineStr">
         <is>
-          <t>Требует уточнения</t>
+          <t>Единая карточка</t>
         </is>
       </c>
       <c r="K101" s="31" t="inlineStr">
         <is>
-          <t>B2B-канал: поставки в магазины при АЗС, не прямая розница</t>
+          <t>Единый каталог; раздел «Элементы питания» для магазинов при АЗС</t>
         </is>
       </c>
       <c r="L101" s="31" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="M101" s="32" t="inlineStr">
         <is>
-          <t>https://rusholts.ru/</t>
+          <t>http://www.rusholts.ru/ru/production/47053342.html</t>
         </is>
       </c>
       <c r="N101" s="31" t="inlineStr">
         <is>
-          <t>Требует проверки глубокой ссылки</t>
+          <t>Проверено</t>
         </is>
       </c>
       <c r="O101" s="30" t="n">
@@ -8409,29 +8409,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9474,7 +9478,7 @@
       </c>
       <c r="D26" s="34" t="inlineStr">
         <is>
-          <t>АБ-Бэттэрис</t>
+          <t>АБ-Бэттэрис (бренд GoPower)</t>
         </is>
       </c>
       <c r="E26" s="33" t="inlineStr">
@@ -9489,12 +9493,12 @@
       </c>
       <c r="G26" s="34" t="inlineStr">
         <is>
-          <t>Оптовый поставщик элементов питания</t>
-        </is>
-      </c>
-      <c r="H26" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Производитель и дистрибьютор элементов питания</t>
+        </is>
+      </c>
+      <c r="H26" s="35" t="inlineStr">
+        <is>
+          <t>https://ab-batteries.ru/catalog/elementy_pitaniya/</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9818,7 @@
       </c>
       <c r="H34" s="35" t="inlineStr">
         <is>
-          <t>https://dixy.ru/</t>
+          <t>https://dixy.ru/catalog/tovary-dlya-doma-i-dachi/osveshchenie-remont-batareyki/</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10298,7 @@
       </c>
       <c r="H46" s="35" t="inlineStr">
         <is>
-          <t>https://relefopt.ru/</t>
+          <t>https://relefopt.ru/catalog/68473/</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10363,7 @@
       </c>
       <c r="E48" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>batkomplekt.ru</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
@@ -10369,12 +10373,12 @@
       </c>
       <c r="G48" s="34" t="inlineStr">
         <is>
-          <t>Оптовый поставщик элементов питания</t>
-        </is>
-      </c>
-      <c r="H48" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Опт электротоваров и товаров народного потребления</t>
+        </is>
+      </c>
+      <c r="H48" s="35" t="inlineStr">
+        <is>
+          <t>https://www.batkomplekt.ru/</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10523,7 @@
       </c>
       <c r="E52" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>istochnik.ru</t>
         </is>
       </c>
       <c r="F52" s="34" t="inlineStr">
@@ -10529,12 +10533,12 @@
       </c>
       <c r="G52" s="34" t="inlineStr">
         <is>
-          <t>Оптовый поставщик элементов питания</t>
-        </is>
-      </c>
-      <c r="H52" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Федеральный дистрибьютор источников питания</t>
+        </is>
+      </c>
+      <c r="H52" s="35" t="inlineStr">
+        <is>
+          <t>https://www.istochnik.ru/</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11018,7 @@
       </c>
       <c r="H64" s="35" t="inlineStr">
         <is>
-          <t>https://sm-komandor.ru/</t>
+          <t>https://delivery.sm-komandor.ru/catalog/batareyki-akkumulyatory_193/</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11643,7 @@
       </c>
       <c r="E80" s="33" t="inlineStr">
         <is>
-          <t>opticom.ru</t>
+          <t>opti-com.ru</t>
         </is>
       </c>
       <c r="F80" s="34" t="inlineStr">
@@ -11654,7 +11658,7 @@
       </c>
       <c r="H80" s="35" t="inlineStr">
         <is>
-          <t>https://opticom.ru/</t>
+          <t>https://www.opti-com.ru/</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12018,7 @@
       </c>
       <c r="H89" s="35" t="inlineStr">
         <is>
-          <t>https://www.sportmaster.ru/</t>
+          <t>https://www.sportmaster.ru/catalog/vidy_sporta_/turizm/ehlektronika-i-navigaciya/akkumulyatory-i-batareyki/</t>
         </is>
       </c>
     </row>
@@ -15694,7 +15698,7 @@
       </c>
       <c r="H181" s="35" t="inlineStr">
         <is>
-          <t>https://sm-komandor.ru/</t>
+          <t>https://delivery.sm-komandor.ru/catalog/batareyki-akkumulyatory_193/</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16698,7 @@
       </c>
       <c r="H206" s="35" t="inlineStr">
         <is>
-          <t>https://www.rs24.ru/</t>
+          <t>https://rs24.ru/product/391260</t>
         </is>
       </c>
     </row>
@@ -19054,7 +19058,7 @@
       </c>
       <c r="H265" s="35" t="inlineStr">
         <is>
-          <t>https://www.ocs.ru/</t>
+          <t>https://www.ocs.ru/vendors/gopower/</t>
         </is>
       </c>
     </row>
@@ -19654,7 +19658,7 @@
       </c>
       <c r="H280" s="35" t="inlineStr">
         <is>
-          <t>https://rusholts.ru/</t>
+          <t>http://www.rusholts.ru/ru/production/47053342.html</t>
         </is>
       </c>
     </row>
@@ -25919,7 +25923,7 @@
       </c>
       <c r="E437" s="33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>vrnbatt.ru</t>
         </is>
       </c>
       <c r="F437" s="34" t="inlineStr">
@@ -25929,12 +25933,12 @@
       </c>
       <c r="G437" s="34" t="inlineStr">
         <is>
-          <t>Региональный поставщик элементов питания</t>
-        </is>
-      </c>
-      <c r="H437" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Опт элементов питания и светотехники</t>
+        </is>
+      </c>
+      <c r="H437" s="35" t="inlineStr">
+        <is>
+          <t>http://vrnbatt.ru/</t>
         </is>
       </c>
     </row>
@@ -26794,12 +26798,12 @@
       </c>
       <c r="D459" s="34" t="inlineStr">
         <is>
-          <t>МТС (салоны)</t>
+          <t>МТС (интернет-магазин)</t>
         </is>
       </c>
       <c r="E459" s="33" t="inlineStr">
         <is>
-          <t>mts.ru</t>
+          <t>shop.mts.ru</t>
         </is>
       </c>
       <c r="F459" s="34" t="inlineStr">
@@ -26814,7 +26818,7 @@
       </c>
       <c r="H459" s="35" t="inlineStr">
         <is>
-          <t>https://www.mts.ru/</t>
+          <t>https://shop.mts.ru/product/batareja-duracell-aa-professional-lr6-bl2</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29178,7 @@
       </c>
       <c r="H518" s="35" t="inlineStr">
         <is>
-          <t>https://www.letu.ru/</t>
+          <t>https://www.letu.ru/product/gp-batteries-elementy-pitaniya-shchelochnye-aaa-lr03-/147100048</t>
         </is>
       </c>
     </row>
@@ -31474,12 +31478,12 @@
       </c>
       <c r="D576" s="34" t="inlineStr">
         <is>
-          <t>Почта России</t>
+          <t>Почта России (Маркет)</t>
         </is>
       </c>
       <c r="E576" s="33" t="inlineStr">
         <is>
-          <t>pochta.ru</t>
+          <t>market.pochta.ru</t>
         </is>
       </c>
       <c r="F576" s="34" t="inlineStr">
@@ -31489,12 +31493,12 @@
       </c>
       <c r="G576" s="34" t="inlineStr">
         <is>
-          <t>Госритейл в отделениях</t>
+          <t>Маркетплейс Почты + продажи в отделениях</t>
         </is>
       </c>
       <c r="H576" s="35" t="inlineStr">
         <is>
-          <t>https://www.pochta.ru/</t>
+          <t>https://market.pochta.ru/</t>
         </is>
       </c>
     </row>
@@ -34318,121 +34322,125 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H364" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H576" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H634" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H640" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H364" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H576" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H634" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H640" r:id="rId136"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
